--- a/backend/data/financials_by_company/1INH.MI.xlsx
+++ b/backend/data/financials_by_company/1INH.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC5"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,216 +697,132 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-427050</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>212765000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-2847000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>53709000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>92695000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>760308000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>215165000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>122470000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-22832000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>26385000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4990000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>61375950</v>
-      </c>
-      <c r="P2" t="n">
-        <v>53709000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1595981000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>126675000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>25957130</v>
-      </c>
-      <c r="U2" t="n">
-        <v>25957130</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>53709000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>53709000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>53709000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-992000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>54701000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>40180000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>54701000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>41384000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>96085000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>-3026000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-3721000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+        <v>-50198000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>359000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>3378000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-13962000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>1437000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>26385000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4990000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>125815000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>835673000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>60123000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>92695000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>92695000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>154644000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>93512000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>61132000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>961488000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>760308000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1721796000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1721796000</v>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>40180000</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-4665876.252505</v>
+        <v>-12081934</v>
       </c>
       <c r="C3" t="n">
-        <v>0.399134</v>
+        <v>0.289</v>
       </c>
       <c r="D3" t="n">
-        <v>261842000</v>
+        <v>218852000</v>
       </c>
       <c r="E3" t="n">
-        <v>-11690000</v>
+        <v>-2440000</v>
       </c>
       <c r="F3" t="n">
-        <v>-11690000</v>
+        <v>-41806000</v>
       </c>
       <c r="G3" t="n">
-        <v>83276000</v>
+        <v>81672000</v>
       </c>
       <c r="H3" t="n">
-        <v>89248000</v>
+        <v>85991000</v>
       </c>
       <c r="I3" t="n">
-        <v>813129000</v>
+        <v>838666000</v>
       </c>
       <c r="J3" t="n">
-        <v>250152000</v>
+        <v>216412000</v>
       </c>
       <c r="K3" t="n">
-        <v>160904000</v>
+        <v>130421000</v>
       </c>
       <c r="L3" t="n">
-        <v>-19576000</v>
+        <v>-13112000</v>
       </c>
       <c r="M3" t="n">
-        <v>21184000</v>
+        <v>14490000</v>
       </c>
       <c r="N3" t="n">
-        <v>1575000</v>
+        <v>1378000</v>
       </c>
       <c r="O3" t="n">
-        <v>90300123.747495</v>
+        <v>150762066</v>
       </c>
       <c r="P3" t="n">
-        <v>55437000</v>
+        <v>-42235000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1636643000</v>
+        <v>1631941000</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>149561000</v>
+        <v>133665000</v>
       </c>
       <c r="T3" t="n">
         <v>26895559</v>
@@ -915,155 +831,157 @@
         <v>26895559</v>
       </c>
       <c r="V3" t="n">
-        <v>2.06</v>
+        <v>-1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>2.06</v>
+        <v>-1.57</v>
       </c>
       <c r="X3" t="n">
-        <v>55437000</v>
+        <v>-42235000</v>
       </c>
       <c r="Y3" t="n">
-        <v>55437000</v>
+        <v>-42235000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>55437000</v>
+        <v>-42235000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-677000</v>
+        <v>-805000</v>
       </c>
       <c r="AC3" t="n">
-        <v>56114000</v>
+        <v>-41430000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-27839000</v>
+        <v>-123907000</v>
       </c>
       <c r="AE3" t="n">
-        <v>83953000</v>
+        <v>82477000</v>
       </c>
       <c r="AF3" t="n">
-        <v>55767000</v>
+        <v>33454000</v>
       </c>
       <c r="AG3" t="n">
-        <v>139720000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>115931000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>121000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>-12263000</v>
+        <v>-41806000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-7057000</v>
+        <v>-6138000</v>
       </c>
       <c r="AK3" t="n">
-        <v>19320000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>3375000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5203000</v>
+      </c>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
-        <v>-33000</v>
-      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>21184000</v>
+        <v>14490000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1575000</v>
+        <v>1378000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>165788000</v>
+        <v>172168000</v>
       </c>
       <c r="AR3" t="n">
-        <v>823514000</v>
+        <v>793275000</v>
       </c>
       <c r="AS3" t="n">
-        <v>59969000</v>
+        <v>57440000</v>
       </c>
       <c r="AT3" t="n">
-        <v>89248000</v>
+        <v>85991000</v>
       </c>
       <c r="AU3" t="n">
-        <v>89248000</v>
+        <v>85991000</v>
       </c>
       <c r="AV3" t="n">
-        <v>158148000</v>
+        <v>160064000</v>
       </c>
       <c r="AW3" t="n">
-        <v>96995000</v>
+        <v>102125000</v>
       </c>
       <c r="AX3" t="n">
-        <v>61153000</v>
+        <v>57939000</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>989302000</v>
+        <v>965443000</v>
       </c>
       <c r="BA3" t="n">
-        <v>813129000</v>
+        <v>838666000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1802431000</v>
+        <v>1804109000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1802431000</v>
+        <v>1804109000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-12081934</v>
+        <v>-4665876.252505</v>
       </c>
       <c r="C4" t="n">
-        <v>0.289</v>
+        <v>0.399134</v>
       </c>
       <c r="D4" t="n">
-        <v>218852000</v>
+        <v>261842000</v>
       </c>
       <c r="E4" t="n">
-        <v>-2440000</v>
+        <v>-11690000</v>
       </c>
       <c r="F4" t="n">
-        <v>-41806000</v>
+        <v>-11690000</v>
       </c>
       <c r="G4" t="n">
-        <v>81672000</v>
+        <v>83276000</v>
       </c>
       <c r="H4" t="n">
-        <v>85991000</v>
+        <v>89248000</v>
       </c>
       <c r="I4" t="n">
-        <v>838666000</v>
+        <v>813129000</v>
       </c>
       <c r="J4" t="n">
-        <v>216412000</v>
+        <v>250152000</v>
       </c>
       <c r="K4" t="n">
-        <v>130421000</v>
+        <v>160904000</v>
       </c>
       <c r="L4" t="n">
-        <v>-13112000</v>
+        <v>-19576000</v>
       </c>
       <c r="M4" t="n">
-        <v>14490000</v>
+        <v>21184000</v>
       </c>
       <c r="N4" t="n">
-        <v>1378000</v>
+        <v>1575000</v>
       </c>
       <c r="O4" t="n">
-        <v>150762066</v>
+        <v>90300123.747495</v>
       </c>
       <c r="P4" t="n">
-        <v>-42235000</v>
+        <v>55437000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1631941000</v>
+        <v>1636643000</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>133665000</v>
+        <v>149561000</v>
       </c>
       <c r="T4" t="n">
         <v>26895559</v>
@@ -1072,267 +990,412 @@
         <v>26895559</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.57</v>
+        <v>2.06</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.57</v>
+        <v>2.06</v>
       </c>
       <c r="X4" t="n">
-        <v>-42235000</v>
+        <v>55437000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-42235000</v>
+        <v>55437000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-42235000</v>
+        <v>55437000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-805000</v>
+        <v>-677000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-41430000</v>
+        <v>56114000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-123907000</v>
+        <v>-27839000</v>
       </c>
       <c r="AE4" t="n">
-        <v>82477000</v>
+        <v>83953000</v>
       </c>
       <c r="AF4" t="n">
-        <v>33454000</v>
+        <v>55767000</v>
       </c>
       <c r="AG4" t="n">
-        <v>115931000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>121000</v>
-      </c>
+        <v>139720000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-41806000</v>
+        <v>-12263000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-6138000</v>
+        <v>-7057000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3375000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>5203000</v>
-      </c>
+        <v>19320000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>-33000</v>
+      </c>
       <c r="AO4" t="n">
-        <v>14490000</v>
+        <v>21184000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1378000</v>
+        <v>1575000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>172168000</v>
+        <v>165788000</v>
       </c>
       <c r="AR4" t="n">
-        <v>793275000</v>
+        <v>823514000</v>
       </c>
       <c r="AS4" t="n">
-        <v>57440000</v>
+        <v>59969000</v>
       </c>
       <c r="AT4" t="n">
-        <v>85991000</v>
+        <v>89248000</v>
       </c>
       <c r="AU4" t="n">
-        <v>85991000</v>
+        <v>89248000</v>
       </c>
       <c r="AV4" t="n">
-        <v>160064000</v>
+        <v>158148000</v>
       </c>
       <c r="AW4" t="n">
-        <v>102125000</v>
+        <v>96995000</v>
       </c>
       <c r="AX4" t="n">
-        <v>57939000</v>
+        <v>61153000</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>965443000</v>
+        <v>989302000</v>
       </c>
       <c r="BA4" t="n">
-        <v>838666000</v>
+        <v>813129000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1804109000</v>
+        <v>1802431000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1804109000</v>
+        <v>1802431000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1035927.339663</v>
+        <v>-427050</v>
       </c>
       <c r="C5" t="n">
-        <v>0.346812</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>252309000</v>
+        <v>212765000</v>
       </c>
       <c r="E5" t="n">
-        <v>-2987000</v>
+        <v>2400000</v>
       </c>
       <c r="F5" t="n">
-        <v>-2987000</v>
+        <v>-2847000</v>
       </c>
       <c r="G5" t="n">
-        <v>97007000</v>
+        <v>53709000</v>
       </c>
       <c r="H5" t="n">
-        <v>85529000</v>
+        <v>92695000</v>
       </c>
       <c r="I5" t="n">
-        <v>731432000</v>
+        <v>760308000</v>
       </c>
       <c r="J5" t="n">
-        <v>249322000</v>
+        <v>215165000</v>
       </c>
       <c r="K5" t="n">
-        <v>163793000</v>
+        <v>122470000</v>
       </c>
       <c r="L5" t="n">
-        <v>-13962000</v>
+        <v>-22832000</v>
       </c>
       <c r="M5" t="n">
-        <v>14124000</v>
+        <v>26385000</v>
       </c>
       <c r="N5" t="n">
-        <v>171000</v>
+        <v>4990000</v>
       </c>
       <c r="O5" t="n">
-        <v>98958072.660337</v>
+        <v>61375950</v>
       </c>
       <c r="P5" t="n">
-        <v>46809000</v>
+        <v>53709000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1469446000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>40180000</v>
-      </c>
+        <v>1595981000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>165626000</v>
+        <v>126675000</v>
       </c>
       <c r="T5" t="n">
-        <v>26332863</v>
+        <v>25957130</v>
       </c>
       <c r="U5" t="n">
-        <v>26332863</v>
+        <v>25957130</v>
       </c>
       <c r="V5" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="X5" t="n">
-        <v>46809000</v>
+        <v>53709000</v>
       </c>
       <c r="Y5" t="n">
-        <v>46809000</v>
+        <v>53709000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>46809000</v>
+        <v>53709000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-755000</v>
+        <v>-992000</v>
       </c>
       <c r="AC5" t="n">
-        <v>47564000</v>
+        <v>54701000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-50198000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>97762000</v>
+        <v>54701000</v>
       </c>
       <c r="AF5" t="n">
-        <v>51907000</v>
+        <v>41384000</v>
       </c>
       <c r="AG5" t="n">
-        <v>149669000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>359000</v>
-      </c>
+        <v>96085000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-2987000</v>
+        <v>-3026000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-2870000</v>
+        <v>-3721000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2479000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>3378000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-13962000</v>
-      </c>
+        <v>1500000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>9000</v>
+        <v>1437000</v>
       </c>
       <c r="AO5" t="n">
-        <v>14124000</v>
+        <v>26385000</v>
       </c>
       <c r="AP5" t="n">
-        <v>171000</v>
+        <v>4990000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>164023000</v>
+        <v>125815000</v>
       </c>
       <c r="AR5" t="n">
-        <v>738014000</v>
+        <v>835673000</v>
       </c>
       <c r="AS5" t="n">
-        <v>58507000</v>
+        <v>60123000</v>
       </c>
       <c r="AT5" t="n">
-        <v>83051000</v>
+        <v>92695000</v>
       </c>
       <c r="AU5" t="n">
-        <v>83051000</v>
+        <v>92695000</v>
       </c>
       <c r="AV5" t="n">
-        <v>134900000</v>
+        <v>154644000</v>
       </c>
       <c r="AW5" t="n">
-        <v>86287000</v>
+        <v>93512000</v>
       </c>
       <c r="AX5" t="n">
-        <v>48613000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>40180000</v>
-      </c>
+        <v>61132000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>902037000</v>
+        <v>961488000</v>
       </c>
       <c r="BA5" t="n">
-        <v>731432000</v>
+        <v>760308000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1633469000</v>
+        <v>1721796000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1633469000</v>
+        <v>1721796000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1519454.430779</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.290028</v>
+      </c>
+      <c r="D6" t="n">
+        <v>212163000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6639000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5239000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>69029000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>93190000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>749048000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>218802000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>125612000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-27336000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>27311000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1588000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>66709454.430779</v>
+      </c>
+      <c r="P6" t="n">
+        <v>69029000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1606472000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>127006000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>24905911</v>
+      </c>
+      <c r="U6" t="n">
+        <v>24905911</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>69029000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>69029000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>69029000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-762000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>69791000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>69791000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>28510000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>98301000</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>5144000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-5162000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-1382000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>-27336000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1613000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>27311000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1588000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>128891000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>857424000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>56460000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>93190000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>93190000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>162475000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>98080000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>64395000</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>986315000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>749048000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1735363000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1735363000</v>
       </c>
     </row>
   </sheetData>
@@ -1346,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ5"/>
+  <dimension ref="A1:CC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1735,242 +1798,118 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1854520</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25041039</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26895559</v>
-      </c>
-      <c r="E2" t="n">
-        <v>449319000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>686593000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>124900000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1292013000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>304900000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>124900000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>92123000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>697543000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1171676000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>699998000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2455000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>697543000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>41741000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>318143000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>69928000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>69928000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1106831000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>641804000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1168000</v>
-      </c>
-      <c r="X2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>3476000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>2517000</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>35538000</v>
+      </c>
+      <c r="BP2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="n">
-        <v>27754000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>77000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>16953000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>54370000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>540628000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>66495000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>474133000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>854000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>465027000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>33650000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>145965000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>25628000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>120337000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>41076000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>42428000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>173421000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>56629000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>33338000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>83454000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1806829000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1036902000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2630000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>13946000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>912000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>912000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>408000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8293000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>572643000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>167348000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>405295000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>430154000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-508454000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>938608000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>17401000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>225578000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>335843000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>64717000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>295069000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>769927000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>19329000</v>
-      </c>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="n">
-        <v>14970000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>395563000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>148390000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>92586000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>154587000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>9345000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>9669000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>175900000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>145151000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>145151000</v>
-      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
@@ -1980,44 +1919,42 @@
         <v>26895559</v>
       </c>
       <c r="E3" t="n">
-        <v>429153000</v>
+        <v>523411000</v>
       </c>
       <c r="F3" t="n">
-        <v>772011000</v>
+        <v>721372000</v>
       </c>
       <c r="G3" t="n">
-        <v>157959000</v>
+        <v>116587000</v>
       </c>
       <c r="H3" t="n">
-        <v>1412933000</v>
+        <v>1343975000</v>
       </c>
       <c r="I3" t="n">
-        <v>439634000</v>
+        <v>390335000</v>
       </c>
       <c r="J3" t="n">
-        <v>157959000</v>
+        <v>116587000</v>
       </c>
       <c r="K3" t="n">
-        <v>77015000</v>
+        <v>70145000</v>
       </c>
       <c r="L3" t="n">
-        <v>717937000</v>
+        <v>692748000</v>
       </c>
       <c r="M3" t="n">
-        <v>1277320000</v>
+        <v>1220547000</v>
       </c>
       <c r="N3" t="n">
-        <v>719661000</v>
+        <v>694808000</v>
       </c>
       <c r="O3" t="n">
-        <v>1724000</v>
+        <v>2060000</v>
       </c>
       <c r="P3" t="n">
-        <v>717937000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+        <v>692748000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>318143000</v>
       </c>
@@ -2028,181 +1965,184 @@
         <v>69928000</v>
       </c>
       <c r="U3" t="n">
-        <v>1209115000</v>
+        <v>1195073000</v>
       </c>
       <c r="V3" t="n">
-        <v>749192000</v>
+        <v>719074000</v>
       </c>
       <c r="W3" t="n">
-        <v>870000</v>
+        <v>882000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>27025000</v>
+        <v>23568000</v>
       </c>
       <c r="Z3" t="n">
-        <v>36000</v>
+        <v>2000</v>
       </c>
       <c r="AA3" t="n">
-        <v>47105000</v>
+        <v>58853000</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>55398000</v>
+        <v>54038000</v>
       </c>
       <c r="AD3" t="n">
-        <v>618162000</v>
+        <v>580638000</v>
       </c>
       <c r="AE3" t="n">
-        <v>58779000</v>
+        <v>52839000</v>
       </c>
       <c r="AF3" t="n">
-        <v>559383000</v>
+        <v>527799000</v>
       </c>
       <c r="AG3" t="n">
-        <v>596000</v>
+        <v>1093000</v>
       </c>
       <c r="AH3" t="n">
-        <v>459923000</v>
+        <v>475999000</v>
       </c>
       <c r="AI3" t="n">
-        <v>31660000</v>
+        <v>38624000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>153849000</v>
+        <v>140734000</v>
       </c>
       <c r="AK3" t="n">
-        <v>18236000</v>
+        <v>17306000</v>
       </c>
       <c r="AL3" t="n">
-        <v>135613000</v>
+        <v>123428000</v>
       </c>
       <c r="AM3" t="n">
-        <v>40495000</v>
+        <v>45520000</v>
       </c>
       <c r="AN3" t="n">
-        <v>41675000</v>
+        <v>42336000</v>
       </c>
       <c r="AO3" t="n">
-        <v>130952000</v>
+        <v>128200000</v>
       </c>
       <c r="AP3" t="n">
-        <v>20990000</v>
+        <v>17606000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>38404000</v>
+        <v>29124000</v>
       </c>
       <c r="AR3" t="n">
-        <v>71558000</v>
+        <v>81470000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1928776000</v>
+        <v>1889881000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1029219000</v>
+        <v>1023547000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2659000</v>
+        <v>1967000</v>
       </c>
       <c r="AV3" t="n">
-        <v>21262000</v>
+        <v>20170000</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>2500000</v>
+        <v>2441000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2500000</v>
+        <v>2441000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5662000</v>
+        <v>4276000</v>
       </c>
       <c r="BA3" t="n">
-        <v>10005000</v>
+        <v>2215000</v>
       </c>
       <c r="BB3" t="n">
-        <v>559978000</v>
+        <v>576161000</v>
       </c>
       <c r="BC3" t="n">
-        <v>164170000</v>
+        <v>172436000</v>
       </c>
       <c r="BD3" t="n">
-        <v>395808000</v>
+        <v>403725000</v>
       </c>
       <c r="BE3" t="n">
-        <v>418306000</v>
+        <v>413187000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-493202000</v>
+        <v>-455041000</v>
       </c>
       <c r="BG3" t="n">
-        <v>911508000</v>
+        <v>868228000</v>
       </c>
       <c r="BH3" t="n">
-        <v>15585000</v>
+        <v>16866000</v>
       </c>
       <c r="BI3" t="n">
-        <v>212313000</v>
+        <v>199661000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>333196000</v>
+        <v>318337000</v>
       </c>
       <c r="BK3" t="n">
-        <v>55699000</v>
+        <v>52678000</v>
       </c>
       <c r="BL3" t="n">
-        <v>294715000</v>
+        <v>280686000</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>899557000</v>
+        <v>866334000</v>
       </c>
       <c r="BO3" t="n">
-        <v>17336000</v>
+        <v>22048000</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>66273000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>21152000</v>
+        <v>18942000</v>
       </c>
       <c r="BR3" t="n">
-        <v>408117000</v>
+        <v>430445000</v>
       </c>
       <c r="BS3" t="n">
-        <v>144113000</v>
+        <v>137645000</v>
       </c>
       <c r="BT3" t="n">
-        <v>97388000</v>
+        <v>118898000</v>
       </c>
       <c r="BU3" t="n">
-        <v>166616000</v>
+        <v>173902000</v>
       </c>
       <c r="BV3" t="n">
-        <v>16864000</v>
+        <v>13381000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5799000</v>
+        <v>5342000</v>
       </c>
       <c r="BX3" t="n">
-        <v>164446000</v>
+        <v>182087000</v>
       </c>
       <c r="BY3" t="n">
-        <v>265843000</v>
+        <v>127816000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>265843000</v>
-      </c>
+        <v>127816000</v>
+      </c>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
@@ -2212,42 +2152,44 @@
         <v>26895559</v>
       </c>
       <c r="E4" t="n">
-        <v>523411000</v>
+        <v>429153000</v>
       </c>
       <c r="F4" t="n">
-        <v>721372000</v>
+        <v>772011000</v>
       </c>
       <c r="G4" t="n">
-        <v>116587000</v>
+        <v>157959000</v>
       </c>
       <c r="H4" t="n">
-        <v>1343975000</v>
+        <v>1412933000</v>
       </c>
       <c r="I4" t="n">
-        <v>390335000</v>
+        <v>439634000</v>
       </c>
       <c r="J4" t="n">
-        <v>116587000</v>
+        <v>157959000</v>
       </c>
       <c r="K4" t="n">
-        <v>70145000</v>
+        <v>77015000</v>
       </c>
       <c r="L4" t="n">
-        <v>692748000</v>
+        <v>717937000</v>
       </c>
       <c r="M4" t="n">
-        <v>1220547000</v>
+        <v>1277320000</v>
       </c>
       <c r="N4" t="n">
-        <v>694808000</v>
+        <v>719661000</v>
       </c>
       <c r="O4" t="n">
-        <v>2060000</v>
+        <v>1724000</v>
       </c>
       <c r="P4" t="n">
-        <v>692748000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>717937000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
         <v>318143000</v>
       </c>
@@ -2258,226 +2200,233 @@
         <v>69928000</v>
       </c>
       <c r="U4" t="n">
-        <v>1195073000</v>
+        <v>1209115000</v>
       </c>
       <c r="V4" t="n">
-        <v>719074000</v>
+        <v>749192000</v>
       </c>
       <c r="W4" t="n">
-        <v>882000</v>
+        <v>870000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>23568000</v>
+        <v>27025000</v>
       </c>
       <c r="Z4" t="n">
-        <v>2000</v>
+        <v>36000</v>
       </c>
       <c r="AA4" t="n">
-        <v>58853000</v>
+        <v>47105000</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>54038000</v>
+        <v>55398000</v>
       </c>
       <c r="AD4" t="n">
-        <v>580638000</v>
+        <v>618162000</v>
       </c>
       <c r="AE4" t="n">
-        <v>52839000</v>
+        <v>58779000</v>
       </c>
       <c r="AF4" t="n">
-        <v>527799000</v>
+        <v>559383000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1093000</v>
+        <v>596000</v>
       </c>
       <c r="AH4" t="n">
-        <v>475999000</v>
+        <v>459923000</v>
       </c>
       <c r="AI4" t="n">
-        <v>38624000</v>
+        <v>31660000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>140734000</v>
+        <v>153849000</v>
       </c>
       <c r="AK4" t="n">
-        <v>17306000</v>
+        <v>18236000</v>
       </c>
       <c r="AL4" t="n">
-        <v>123428000</v>
+        <v>135613000</v>
       </c>
       <c r="AM4" t="n">
-        <v>45520000</v>
+        <v>40495000</v>
       </c>
       <c r="AN4" t="n">
-        <v>42336000</v>
+        <v>41675000</v>
       </c>
       <c r="AO4" t="n">
-        <v>128200000</v>
+        <v>130952000</v>
       </c>
       <c r="AP4" t="n">
-        <v>17606000</v>
+        <v>20990000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29124000</v>
+        <v>38404000</v>
       </c>
       <c r="AR4" t="n">
-        <v>81470000</v>
+        <v>71558000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1889881000</v>
+        <v>1928776000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1023547000</v>
+        <v>1029219000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1967000</v>
+        <v>2659000</v>
       </c>
       <c r="AV4" t="n">
-        <v>20170000</v>
+        <v>21262000</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>2441000</v>
+        <v>2500000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2441000</v>
+        <v>2500000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4276000</v>
+        <v>5662000</v>
       </c>
       <c r="BA4" t="n">
-        <v>2215000</v>
+        <v>10005000</v>
       </c>
       <c r="BB4" t="n">
-        <v>576161000</v>
+        <v>559978000</v>
       </c>
       <c r="BC4" t="n">
-        <v>172436000</v>
+        <v>164170000</v>
       </c>
       <c r="BD4" t="n">
-        <v>403725000</v>
+        <v>395808000</v>
       </c>
       <c r="BE4" t="n">
-        <v>413187000</v>
+        <v>418306000</v>
       </c>
       <c r="BF4" t="n">
-        <v>-455041000</v>
+        <v>-493202000</v>
       </c>
       <c r="BG4" t="n">
-        <v>868228000</v>
+        <v>911508000</v>
       </c>
       <c r="BH4" t="n">
-        <v>16866000</v>
+        <v>15585000</v>
       </c>
       <c r="BI4" t="n">
-        <v>199661000</v>
+        <v>212313000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>318337000</v>
+        <v>333196000</v>
       </c>
       <c r="BK4" t="n">
-        <v>52678000</v>
+        <v>55699000</v>
       </c>
       <c r="BL4" t="n">
-        <v>280686000</v>
+        <v>294715000</v>
       </c>
       <c r="BM4" t="n">
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>866334000</v>
+        <v>899557000</v>
       </c>
       <c r="BO4" t="n">
-        <v>22048000</v>
+        <v>17336000</v>
       </c>
       <c r="BP4" t="n">
-        <v>66273000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>18942000</v>
+        <v>21152000</v>
       </c>
       <c r="BR4" t="n">
-        <v>430445000</v>
+        <v>408117000</v>
       </c>
       <c r="BS4" t="n">
-        <v>137645000</v>
+        <v>144113000</v>
       </c>
       <c r="BT4" t="n">
-        <v>118898000</v>
+        <v>97388000</v>
       </c>
       <c r="BU4" t="n">
-        <v>173902000</v>
+        <v>166616000</v>
       </c>
       <c r="BV4" t="n">
-        <v>13381000</v>
+        <v>16864000</v>
       </c>
       <c r="BW4" t="n">
-        <v>5342000</v>
+        <v>5799000</v>
       </c>
       <c r="BX4" t="n">
-        <v>182087000</v>
+        <v>164446000</v>
       </c>
       <c r="BY4" t="n">
-        <v>127816000</v>
+        <v>265843000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>127816000</v>
-      </c>
+        <v>265843000</v>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1854520</v>
+      </c>
       <c r="C5" t="n">
-        <v>26895559</v>
+        <v>25041039</v>
       </c>
       <c r="D5" t="n">
         <v>26895559</v>
       </c>
       <c r="E5" t="n">
-        <v>409009000</v>
+        <v>449319000</v>
       </c>
       <c r="F5" t="n">
-        <v>640454000</v>
+        <v>686593000</v>
       </c>
       <c r="G5" t="n">
-        <v>233016000</v>
+        <v>124900000</v>
       </c>
       <c r="H5" t="n">
-        <v>1330960000</v>
+        <v>1292013000</v>
       </c>
       <c r="I5" t="n">
-        <v>304080000</v>
+        <v>304900000</v>
       </c>
       <c r="J5" t="n">
-        <v>233016000</v>
+        <v>124900000</v>
       </c>
       <c r="K5" t="n">
-        <v>95125000</v>
+        <v>92123000</v>
       </c>
       <c r="L5" t="n">
-        <v>785631000</v>
+        <v>697543000</v>
       </c>
       <c r="M5" t="n">
-        <v>1193891000</v>
+        <v>1171676000</v>
       </c>
       <c r="N5" t="n">
-        <v>787474000</v>
+        <v>699998000</v>
       </c>
       <c r="O5" t="n">
-        <v>1843000</v>
+        <v>2455000</v>
       </c>
       <c r="P5" t="n">
-        <v>785631000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>697543000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>41741000</v>
+      </c>
       <c r="R5" t="n">
         <v>318143000</v>
       </c>
@@ -2488,178 +2437,420 @@
         <v>69928000</v>
       </c>
       <c r="U5" t="n">
-        <v>1069935000</v>
+        <v>1106831000</v>
       </c>
       <c r="V5" t="n">
-        <v>615634000</v>
+        <v>641804000</v>
       </c>
       <c r="W5" t="n">
-        <v>2262000</v>
+        <v>1168000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>41321000</v>
+        <v>27754000</v>
       </c>
       <c r="Z5" t="n">
-        <v>168000</v>
+        <v>77000</v>
       </c>
       <c r="AA5" t="n">
-        <v>44593000</v>
+        <v>16953000</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>48569000</v>
+        <v>54370000</v>
       </c>
       <c r="AD5" t="n">
-        <v>477286000</v>
+        <v>540628000</v>
       </c>
       <c r="AE5" t="n">
-        <v>69026000</v>
+        <v>66495000</v>
       </c>
       <c r="AF5" t="n">
-        <v>408260000</v>
+        <v>474133000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1435000</v>
+        <v>854000</v>
       </c>
       <c r="AH5" t="n">
-        <v>454301000</v>
+        <v>465027000</v>
       </c>
       <c r="AI5" t="n">
-        <v>76478000</v>
+        <v>33650000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>163168000</v>
+        <v>145965000</v>
       </c>
       <c r="AK5" t="n">
-        <v>26099000</v>
+        <v>25628000</v>
       </c>
       <c r="AL5" t="n">
-        <v>137069000</v>
+        <v>120337000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2356000</v>
+        <v>41076000</v>
       </c>
       <c r="AN5" t="n">
-        <v>45727000</v>
+        <v>42428000</v>
       </c>
       <c r="AO5" t="n">
-        <v>132122000</v>
+        <v>173421000</v>
       </c>
       <c r="AP5" t="n">
-        <v>19594000</v>
+        <v>56629000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24931000</v>
+        <v>33338000</v>
       </c>
       <c r="AR5" t="n">
-        <v>87597000</v>
+        <v>83454000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1857409000</v>
+        <v>1806829000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1099028000</v>
+        <v>1036902000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3476000</v>
+        <v>2630000</v>
       </c>
       <c r="AV5" t="n">
-        <v>13771000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2517000</v>
-      </c>
+        <v>13946000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>2517000</v>
+        <v>2899000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2517000</v>
+        <v>2899000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4578000</v>
+        <v>408000</v>
       </c>
       <c r="BA5" t="n">
-        <v>5782000</v>
+        <v>8293000</v>
       </c>
       <c r="BB5" t="n">
-        <v>552615000</v>
+        <v>572643000</v>
       </c>
       <c r="BC5" t="n">
-        <v>142817000</v>
+        <v>167348000</v>
       </c>
       <c r="BD5" t="n">
-        <v>409798000</v>
+        <v>405295000</v>
       </c>
       <c r="BE5" t="n">
-        <v>510012000</v>
+        <v>430154000</v>
       </c>
       <c r="BF5" t="n">
-        <v>-572214000</v>
+        <v>-508454000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1082226000</v>
+        <v>938608000</v>
       </c>
       <c r="BH5" t="n">
-        <v>28972000</v>
+        <v>17401000</v>
       </c>
       <c r="BI5" t="n">
-        <v>654308000</v>
+        <v>225578000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6595000</v>
+        <v>335843000</v>
       </c>
       <c r="BK5" t="n">
-        <v>76441000</v>
+        <v>64717000</v>
       </c>
       <c r="BL5" t="n">
-        <v>315910000</v>
+        <v>295069000</v>
       </c>
       <c r="BM5" t="n">
         <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>758381000</v>
+        <v>769927000</v>
       </c>
       <c r="BO5" t="n">
-        <v>35538000</v>
-      </c>
-      <c r="BP5" t="n">
+        <v>19329000</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="n">
+        <v>14970000</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>395563000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>148390000</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>92586000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>154587000</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>16545000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>11378000</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>175900000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>155140000</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>145151000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>0</v>
       </c>
-      <c r="BQ5" t="n">
-        <v>22246000</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>381648000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>118854000</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>102205000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>160589000</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>15244000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>13739000</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>153646000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>136320000</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>136320000</v>
+      <c r="CB5" t="n">
+        <v>431000</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>9989000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>904441</v>
+      </c>
+      <c r="C6" t="n">
+        <v>24895559</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>455872000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>761638000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>158605000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1402902000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>442440000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>158605000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88160000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>729424000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1307948000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>730714000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>729424000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>20260000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>318143000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>69928000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>69928000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1173576000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>749355000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2279000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>25274000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>62000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23353000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>52486000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>645194000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>66670000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>578524000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>707000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>424221000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>26791000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>116444000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>21490000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>94954000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>44296000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>39728000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>140293000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>28624000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>29173000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>82496000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1904290000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1037629000</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>12817000</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>2436000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2436000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>663000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7276000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>570819000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>163899000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>406920000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>438769000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-530163000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>968932000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>17114000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>232860000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>341000000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>61061000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>316897000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>866661000</v>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="n">
+        <v>23386000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>400923000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>143607000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>94641000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>162675000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>19602000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>26285000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>170969000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>225027000</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>217606000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>469000</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>7421000</v>
       </c>
     </row>
   </sheetData>
@@ -2673,7 +2864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2915,562 +3106,620 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>92779000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-41741000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-135012000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35232000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>-50903000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>145151000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>84667000</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>265843000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>873000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-121565000</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-199879000</v>
-      </c>
+        <v>-69784000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-5200000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-30955000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-41741000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-41741000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>-99780000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-99780000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-135012000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>35232000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-65368000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>15741000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-807000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-807000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-29399000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>-29399000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-10567000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-10567000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-40336000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-40336000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>143682000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-50106000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>5104000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-32676000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1515000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-4963000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-28479000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23876000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>41384000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>92695000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>92695000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-3119000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>54701000</v>
-      </c>
+        <v>-671000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>84667000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>7849000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>155708000</v>
-      </c>
-      <c r="C3" t="n">
+        <v>61799000</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>-157789000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>264061000</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
-        <v>-126596000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>168732000</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-61949000</v>
+        <v>-54540000</v>
       </c>
       <c r="H3" t="n">
-        <v>265843000</v>
+        <v>127816000</v>
       </c>
       <c r="I3" t="n">
-        <v>-3704000</v>
+        <v>-5128000</v>
       </c>
       <c r="J3" t="n">
-        <v>127816000</v>
+        <v>136320000</v>
       </c>
       <c r="K3" t="n">
-        <v>-753000</v>
+        <v>-262000</v>
       </c>
       <c r="L3" t="n">
-        <v>142484000</v>
+        <v>-3114000</v>
       </c>
       <c r="M3" t="n">
-        <v>-24589000</v>
+        <v>-80920000</v>
       </c>
       <c r="N3" t="n">
-        <v>-501000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>55905000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-2297000</v>
+      </c>
       <c r="P3" t="n">
-        <v>-21516000</v>
+        <v>-28240000</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>42136000</v>
+        <v>106272000</v>
       </c>
       <c r="U3" t="n">
-        <v>42136000</v>
+        <v>106272000</v>
       </c>
       <c r="V3" t="n">
-        <v>-126596000</v>
+        <v>-157789000</v>
       </c>
       <c r="W3" t="n">
-        <v>168732000</v>
+        <v>264061000</v>
       </c>
       <c r="X3" t="n">
-        <v>-50083000</v>
+        <v>-94438000</v>
       </c>
       <c r="Y3" t="n">
-        <v>21318000</v>
+        <v>9445000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-601000</v>
+        <v>-417000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-601000</v>
+        <v>-417000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-8851000</v>
+        <v>-48926000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9843000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-8851000</v>
+        <v>-58769000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-10816000</v>
+        <v>-8047000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-10816000</v>
+        <v>-8047000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-51133000</v>
+        <v>-46493000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-51133000</v>
+        <v>-46493000</v>
       </c>
       <c r="AI3" t="n">
-        <v>217657000</v>
+        <v>116339000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-48089000</v>
+        <v>-48454000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2068000</v>
+        <v>1378000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-24533000</v>
+        <v>-22162000</v>
       </c>
       <c r="AM3" t="n">
-        <v>50000</v>
+        <v>71000</v>
       </c>
       <c r="AN3" t="n">
-        <v>28414000</v>
+        <v>-73036000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-3374000</v>
+        <v>9932000</v>
       </c>
       <c r="AP3" t="n">
-        <v>35349000</v>
+        <v>-94341000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12283000</v>
+        <v>17750000</v>
       </c>
       <c r="AR3" t="n">
-        <v>55767000</v>
+        <v>33454000</v>
       </c>
       <c r="AS3" t="n">
-        <v>89248000</v>
+        <v>85991000</v>
       </c>
       <c r="AT3" t="n">
-        <v>89248000</v>
+        <v>85991000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-824000</v>
+        <v>-3902000</v>
       </c>
       <c r="AV3" t="n">
-        <v>83953000</v>
+        <v>82477000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>61799000</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>155708000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" t="n">
-        <v>-157789000</v>
+        <v>-126596000</v>
       </c>
       <c r="E4" t="n">
-        <v>264061000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+        <v>168732000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-54540000</v>
+        <v>-61949000</v>
       </c>
       <c r="H4" t="n">
+        <v>265843000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-3704000</v>
+      </c>
+      <c r="J4" t="n">
         <v>127816000</v>
       </c>
-      <c r="I4" t="n">
-        <v>-5128000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>136320000</v>
-      </c>
       <c r="K4" t="n">
-        <v>-262000</v>
+        <v>-753000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3114000</v>
+        <v>142484000</v>
       </c>
       <c r="M4" t="n">
-        <v>-80920000</v>
+        <v>-24589000</v>
       </c>
       <c r="N4" t="n">
-        <v>55905000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-2297000</v>
-      </c>
+        <v>-501000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-28240000</v>
+        <v>-21516000</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
+      <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>106272000</v>
+        <v>42136000</v>
       </c>
       <c r="U4" t="n">
-        <v>106272000</v>
+        <v>42136000</v>
       </c>
       <c r="V4" t="n">
-        <v>-157789000</v>
+        <v>-126596000</v>
       </c>
       <c r="W4" t="n">
-        <v>264061000</v>
+        <v>168732000</v>
       </c>
       <c r="X4" t="n">
-        <v>-94438000</v>
+        <v>-50083000</v>
       </c>
       <c r="Y4" t="n">
-        <v>9445000</v>
+        <v>21318000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-417000</v>
+        <v>-601000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-417000</v>
+        <v>-601000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-48926000</v>
+        <v>-8851000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9843000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-58769000</v>
+        <v>-8851000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-8047000</v>
+        <v>-10816000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-8047000</v>
+        <v>-10816000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-46493000</v>
+        <v>-51133000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-46493000</v>
+        <v>-51133000</v>
       </c>
       <c r="AI4" t="n">
-        <v>116339000</v>
+        <v>217657000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-48454000</v>
+        <v>-48089000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1378000</v>
+        <v>2068000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-22162000</v>
+        <v>-24533000</v>
       </c>
       <c r="AM4" t="n">
-        <v>71000</v>
+        <v>50000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-73036000</v>
+        <v>28414000</v>
       </c>
       <c r="AO4" t="n">
-        <v>9932000</v>
+        <v>-3374000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-94341000</v>
+        <v>35349000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17750000</v>
+        <v>12283000</v>
       </c>
       <c r="AR4" t="n">
-        <v>33454000</v>
+        <v>55767000</v>
       </c>
       <c r="AS4" t="n">
-        <v>85991000</v>
+        <v>89248000</v>
       </c>
       <c r="AT4" t="n">
-        <v>85991000</v>
+        <v>89248000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-3902000</v>
+        <v>-824000</v>
       </c>
       <c r="AV4" t="n">
-        <v>82477000</v>
+        <v>83953000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>105802000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>92779000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-41741000</v>
+      </c>
       <c r="D5" t="n">
-        <v>-142599000</v>
+        <v>-135012000</v>
       </c>
       <c r="E5" t="n">
-        <v>57500000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>84667000</v>
-      </c>
+        <v>35232000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-52553000</v>
+        <v>-50903000</v>
       </c>
       <c r="H5" t="n">
-        <v>136320000</v>
+        <v>145151000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>194701000</v>
+        <v>265843000</v>
       </c>
       <c r="K5" t="n">
-        <v>-122000</v>
+        <v>873000</v>
       </c>
       <c r="L5" t="n">
-        <v>-58259000</v>
+        <v>-121565000</v>
       </c>
       <c r="M5" t="n">
-        <v>-69784000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-40840000</v>
+        <v>-199879000</v>
       </c>
       <c r="O5" t="n">
-        <v>-671000</v>
+        <v>-5200000</v>
       </c>
       <c r="P5" t="n">
-        <v>-21517000</v>
+        <v>-30955000</v>
       </c>
       <c r="Q5" t="n">
-        <v>84667000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>84667000</v>
-      </c>
+        <v>-41741000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-41741000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-85099000</v>
+        <v>-99780000</v>
       </c>
       <c r="U5" t="n">
-        <v>-85099000</v>
+        <v>-99780000</v>
       </c>
       <c r="V5" t="n">
-        <v>-142599000</v>
+        <v>-135012000</v>
       </c>
       <c r="W5" t="n">
-        <v>57500000</v>
+        <v>35232000</v>
       </c>
       <c r="X5" t="n">
-        <v>-105990000</v>
+        <v>-65368000</v>
       </c>
       <c r="Y5" t="n">
-        <v>6764000</v>
+        <v>15741000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-722000</v>
+        <v>-807000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-722000</v>
+        <v>-807000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-59479000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7849000</v>
-      </c>
+        <v>-29399000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-67328000</v>
+        <v>-29399000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6965000</v>
+        <v>-10567000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-6965000</v>
+        <v>-10567000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-45588000</v>
+        <v>-40336000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-45588000</v>
+        <v>-40336000</v>
       </c>
       <c r="AI5" t="n">
-        <v>158355000</v>
+        <v>143682000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-44496000</v>
+        <v>-50106000</v>
       </c>
       <c r="AK5" t="n">
-        <v>187000</v>
+        <v>5104000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-19575000</v>
+        <v>-32676000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1244000</v>
+        <v>1515000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-29246000</v>
+        <v>-4963000</v>
       </c>
       <c r="AO5" t="n">
-        <v>38087000</v>
+        <v>-28479000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-73040000</v>
+        <v>23876000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17034000</v>
+        <v>32400000</v>
       </c>
       <c r="AR5" t="n">
-        <v>51907000</v>
+        <v>41384000</v>
       </c>
       <c r="AS5" t="n">
-        <v>85529000</v>
+        <v>92695000</v>
       </c>
       <c r="AT5" t="n">
-        <v>85529000</v>
+        <v>92695000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1991000</v>
+        <v>-3119000</v>
       </c>
       <c r="AV5" t="n">
-        <v>97762000</v>
+        <v>54701000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89618000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-3061000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-163052000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>239780000</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>-60567000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>217606000</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>145151000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-2858000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>75313000</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>-2551000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-17274000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-29875000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-3061000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-3061000</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>76728000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>76728000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-163052000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>239780000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-72321000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7901000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-620000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-620000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-19035000</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>-19035000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-12199000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-12199000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-48368000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-48368000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>150185000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-53982000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1593000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-28667000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>13725000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>17687000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>29202000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>28510000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>93190000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>93190000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-3275000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>69791000</v>
       </c>
     </row>
   </sheetData>
@@ -3484,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EV2"/>
+  <dimension ref="A1:ER2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3660,590 +3909,570 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>marketState</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>shortName</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
-          <t>marketState</t>
+          <t>longName</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>shortName</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
       <c r="ER1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4260,10 +4489,8 @@
           <t>Bergisch Gladbach</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>51429</t>
-        </is>
+      <c r="C2" t="n">
+        <v>51429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4344,7 +4571,7 @@
         <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1767139200</v>
@@ -4361,425 +4588,413 @@
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>30.8</v>
+        <v>26.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>30.8</v>
+        <v>26.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>30.8</v>
+        <v>26.85</v>
       </c>
       <c r="AE2" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>30.8</v>
+        <v>26.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>30.8</v>
+        <v>26.85</v>
       </c>
       <c r="AH2" t="n">
-        <v>30.8</v>
+        <v>26.85</v>
       </c>
       <c r="AI2" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>9.946043</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>124</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>83</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>739639680</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>749002212</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.41554472</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>29.356</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="BA2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="BB2" t="n">
+        <v>0.04676259</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1351753984</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.03881</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>21052556</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>26750079</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.18197</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.23493999</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>26750079</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>30.078</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.91927654</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>69079000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6.289</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.29756093</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BY2" t="n">
         <v>1780531200</v>
       </c>
-      <c r="AL2" t="n">
-        <v>0.45450002</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>11.193181</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>134</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>127</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>127</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>790464832</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>782439810</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>20.05</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.4440993</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>29.377</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>27.044</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.044520546</v>
-      </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="CA2" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CC2" t="n">
+        <v>119759000</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>214940992</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>773036992</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1779928064</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>103.043</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>71.496</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.048130002</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0.09531999400000001</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1010516992</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>27634250</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>98609000</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0.56773</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.12076</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.08130999999999999</v>
+      </c>
+      <c r="CV2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="BH2" t="b">
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>1INH.MI</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DB2" t="b">
         <v>0</v>
       </c>
-      <c r="BI2" t="n">
-        <v>1390342784</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.03881</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>21052556</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>26750079</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.18197</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.20677</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>26750079</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>30.078</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0.98244566</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>69079000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>6.468</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.43632078</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1780531200</v>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CE2" t="n">
-        <v>29.55</v>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CG2" t="n">
-        <v>119759000</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>214940992</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>773036992</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.976</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>1779928064</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>103.043</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>71.496</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.048130002</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0.09531999400000001</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1010516992</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>27634250</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>98609000</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.56773</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.12076</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>0.08130999999999999</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>1INH.MI</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>1781009909</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>INDUS HOLDING</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>INDUS Holding AG</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>finmb_4481923</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>INDUS HOLDING</t>
-        </is>
-      </c>
-      <c r="DJ2" t="b">
+      <c r="DP2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="n">
-        <v>1.198625</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>29.55</v>
-      </c>
-      <c r="DM2" t="b">
+      <c r="DQ2" t="n">
+        <v>1708588800000</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.14999962</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>26.85 - 26.85</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>124</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>7.1499996</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.34878048</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>20.5 - 33.5</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-5.8500004</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.17462687</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>29.756092</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1786548600</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1786548600</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1786548600</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1723537800</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1723537800</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.539567</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="EI2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="n">
-        <v>1708588800000</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.34999847</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>30.8 - 30.8</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>134</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>9.049999</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.44146338</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>20.5 - 33.5</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>-3.9500008</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.11791047</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>43.63208</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1786548600</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1786548600</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1786548600</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1723537800</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1723537800</v>
-      </c>
-      <c r="ED2" t="b">
+      <c r="EJ2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-1.7060013</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.058114227</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.23999977</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0.00875592</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>20</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EQ2" t="b">
         <v>0</v>
       </c>
-      <c r="EE2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.17299843</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.0058889072</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>2.5059986</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.09266375</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>INDUS Holding AG</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>[{'header': 'Dividend', 'message': '1INH.MI announced a cash dividend of EUR 1.30 with an ex-date of Jun. 4, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1780524000000, 'amount': '1.30'}}]</t>
-        </is>
-      </c>
-      <c r="EN2" t="n">
-        <v>1779979163</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>finmb_4481923</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="EU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EV2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
